--- a/website/examples/example_odk_attestation.anchor_bundle.xlsx
+++ b/website/examples/example_odk_attestation.anchor_bundle.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R0471a1ed5ec24d1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R6a0aeef4aa534572"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rd65980254f5e434f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R016bf30d255b4f96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rdcdc37c77e3a44c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rb098947cf5834d6b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -430,7 +430,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>researchos_attestation_test</x:v>
+        <x:v>methodmesh_attestation_test</x:v>
       </x:c>
       <x:c r="G3" s="11"/>
       <x:c r="H3" s="11"/>
@@ -479,7 +479,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='attestation.anchor_bundle',input_study_id=${study_id_input},operator_id=${operator_id_input},return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='attestation.anchor_bundle',input_study_id=${study_id_input},operator_id=${operator_id_input},return_mode='flat')</x:v>
       </x:c>
       <x:c r="J5" s="11"/>
       <x:c r="K5" s="11"/>
@@ -489,10 +489,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>researchos_execution_id</x:v>
+        <x:v>methodmesh_execution_id</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>ResearchOS execution ID</x:v>
+        <x:v>MethodMesh execution ID</x:v>
       </x:c>
       <x:c r="D6" s="11"/>
       <x:c r="E6" s="11"/>
@@ -510,10 +510,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>researchos_method_id</x:v>
+        <x:v>methodmesh_method_id</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>ResearchOS method ID</x:v>
+        <x:v>MethodMesh method ID</x:v>
       </x:c>
       <x:c r="D7" s="11"/>
       <x:c r="E7" s="11"/>
@@ -531,10 +531,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>researchos_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>ResearchOS status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D8" s="11"/>
       <x:c r="E8" s="11"/>
